--- a/src/test/resources/Data/GoldData.xlsx
+++ b/src/test/resources/Data/GoldData.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -213,6 +213,12 @@
   </si>
   <si>
     <t>The price of gold in India today is ₹15,644 per gram for 24 karat gold, ₹14,340 per gram for 22 karat gold and ₹11,733 per gram for 18 karat gold (also called 999 gold).</t>
+  </si>
+  <si>
+    <t>05-03-2026</t>
+  </si>
+  <si>
+    <t>Today's gold price in India stands at ₹16,353 per gram for 24 karat gold (99.9% purity), ₹14,990 per gram for 22 karat gold (91.6% purity), and ₹12,265 per gram for 18 karat gold (75% purity).</t>
   </si>
 </sst>
 </file>
@@ -614,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1874148-A194-473D-9A92-69152072B55A}">
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="13.109375"/>
@@ -950,6 +956,30 @@
         <v>58</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="s" s="3">
+        <v>59</v>
+      </c>
+      <c r="B42" t="s" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="3">
+        <v>59</v>
+      </c>
+      <c r="B43" t="s" s="4">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="3">
+        <v>59</v>
+      </c>
+      <c r="B44" t="s" s="4">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
